--- a/materiais_relatorio/comparacao_graficos.xlsx
+++ b/materiais_relatorio/comparacao_graficos.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="8">
   <si>
     <t>Ordered Input</t>
   </si>
@@ -23,6 +23,9 @@
   </si>
   <si>
     <t>Selectionsort</t>
+  </si>
+  <si>
+    <t>Insertionsort</t>
   </si>
   <si>
     <t>Heapsort</t>
@@ -38,7 +41,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -55,6 +58,17 @@
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -115,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -128,11 +142,17 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -140,14 +160,17 @@
     <xf borderId="4" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -181,7 +204,7 @@
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
               </a:rPr>
-              <a:t>Ordered Input</a:t>
+              <a:t>Reverse Ordered</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -196,7 +219,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Página1'!$B$2:$B$3</c:f>
+              <c:f>'Página1'!$C$21</c:f>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -211,23 +234,23 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Página1'!$A$4:$A$18</c:f>
+              <c:f>'Página1'!$B$22:$B$36</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Página1'!$B$4:$B$18</c:f>
+              <c:f>'Página1'!$C$22:$C$36</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Página1'!$C$2:$C$3</c:f>
+              <c:f>'Página1'!$D$21</c:f>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -242,23 +265,23 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Página1'!$A$4:$A$18</c:f>
+              <c:f>'Página1'!$B$22:$B$36</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Página1'!$C$4:$C$18</c:f>
+              <c:f>'Página1'!$D$22:$D$36</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Página1'!$D$2:$D$3</c:f>
+              <c:f>'Página1'!$E$21</c:f>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -273,22 +296,53 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Página1'!$A$4:$A$18</c:f>
+              <c:f>'Página1'!$B$22:$B$36</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Página1'!$D$4:$D$18</c:f>
+              <c:f>'Página1'!$E$22:$E$36</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="107412357"/>
-        <c:axId val="1237093095"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Página1'!$F$21</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="34A853"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Página1'!$B$22:$B$36</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Página1'!$F$22:$F$36</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:axId val="574485113"/>
+        <c:axId val="1873004489"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="107412357"/>
+        <c:axId val="574485113"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -340,10 +394,648 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1237093095"/>
+        <c:crossAx val="1873004489"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1237093095"/>
+        <c:axId val="1873004489"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="7.5E7"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="574485113"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Uniform Input</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Página1'!$C$39</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="4285F4"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Página1'!$B$40:$B$54</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Página1'!$C$40:$C$54</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Página1'!$D$39</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="EA4335"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Página1'!$B$40:$B$54</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Página1'!$D$40:$D$54</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Página1'!$E$39</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="FBBC04"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Página1'!$B$40:$B$54</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Página1'!$E$40:$E$54</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Página1'!$F$39</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="34A853"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Página1'!$B$40:$B$54</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Página1'!$F$40:$F$54</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:axId val="1518612996"/>
+        <c:axId val="1087632442"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1518612996"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Vetor</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1087632442"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1087632442"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="4000000.0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1518612996"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Ordered Input</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Página1'!$C$3</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="4285F4"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Página1'!$B$4:$B$18</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Página1'!$C$4:$C$18</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Página1'!$D$3</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="EA4335"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Página1'!$B$4:$B$18</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Página1'!$D$4:$D$18</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Página1'!$E$3</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="FBBC04"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Página1'!$B$4:$B$18</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Página1'!$E$4:$E$18</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Página1'!$F$3</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="34A853"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Página1'!$B$4:$B$18</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Página1'!$F$4:$F$18</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:axId val="797437698"/>
+        <c:axId val="188258678"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="797437698"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Vetor</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="188258678"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="188258678"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -418,581 +1110,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="107412357"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0">
-            <a:defRPr b="0">
-              <a:solidFill>
-                <a:srgbClr val="1A1A1A"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-  </c:chart>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0">
-                <a:solidFill>
-                  <a:srgbClr val="757575"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="0">
-                <a:solidFill>
-                  <a:srgbClr val="757575"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:rPr>
-              <a:t>Reverse Ordered</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Página1'!$B$21</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln cmpd="sng">
-              <a:solidFill>
-                <a:srgbClr val="4285F4"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Página1'!$A$22:$A$36</c:f>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Página1'!$B$22:$B$36</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Página1'!$C$21</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln cmpd="sng">
-              <a:solidFill>
-                <a:srgbClr val="EA4335"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Página1'!$A$22:$A$36</c:f>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Página1'!$C$22:$C$36</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Página1'!$D$21</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln cmpd="sng">
-              <a:solidFill>
-                <a:srgbClr val="FBBC04"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Página1'!$A$22:$A$36</c:f>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Página1'!$D$22:$D$36</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:axId val="894212309"/>
-        <c:axId val="271124979"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="894212309"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t>Vetor</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:spPr/>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="271124979"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="271124979"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="B7B7B7"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC">
-                  <a:alpha val="0"/>
-                </a:srgbClr>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:minorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="894212309"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0">
-            <a:defRPr b="0">
-              <a:solidFill>
-                <a:srgbClr val="1A1A1A"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-  </c:chart>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0">
-                <a:solidFill>
-                  <a:srgbClr val="757575"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="0">
-                <a:solidFill>
-                  <a:srgbClr val="757575"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:rPr>
-              <a:t>Uniform Input</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Página1'!$B$39</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln cmpd="sng">
-              <a:solidFill>
-                <a:srgbClr val="4285F4"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Página1'!$A$40:$A$54</c:f>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Página1'!$B$40:$B$54</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Página1'!$C$39</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln cmpd="sng">
-              <a:solidFill>
-                <a:srgbClr val="EA4335"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Página1'!$A$40:$A$54</c:f>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Página1'!$C$40:$C$54</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Página1'!$D$39</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln cmpd="sng">
-              <a:solidFill>
-                <a:srgbClr val="FBBC04"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Página1'!$A$40:$A$54</c:f>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Página1'!$D$40:$D$54</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:axId val="1666125300"/>
-        <c:axId val="976559873"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1666125300"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t>Vetor</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:spPr/>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="976559873"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="976559873"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="B7B7B7"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC">
-                  <a:alpha val="0"/>
-                </a:srgbClr>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:minorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1666125300"/>
+        <c:crossAx val="797437698"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1022,10 +1140,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>933450</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5715000" cy="3533775"/>
     <xdr:graphicFrame>
@@ -1047,10 +1165,10 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>933450</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5715000" cy="3533775"/>
     <xdr:graphicFrame>
@@ -1072,10 +1190,10 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>933450</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5715000" cy="3533775"/>
     <xdr:graphicFrame>
@@ -1304,212 +1422,288 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>4</v>
       </c>
+      <c r="F3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="N3" s="7"/>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="2"/>
+      <c r="B4" s="8">
         <v>10000.0</v>
       </c>
-      <c r="B4" s="7">
+      <c r="C4" s="9">
         <v>1000.0</v>
       </c>
-      <c r="C4" s="7">
+      <c r="D4" s="9">
         <v>352000.0</v>
       </c>
-      <c r="D4" s="7">
+      <c r="E4" s="9">
+        <v>1000.0</v>
+      </c>
+      <c r="F4" s="9">
         <v>3000.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6">
+      <c r="A5" s="2"/>
+      <c r="B5" s="8">
         <v>50000.0</v>
       </c>
-      <c r="B5" s="7">
+      <c r="C5" s="9">
         <v>4000.0</v>
       </c>
-      <c r="C5" s="7">
+      <c r="D5" s="9">
         <v>8969000.0</v>
       </c>
-      <c r="D5" s="7">
+      <c r="E5" s="9">
+        <v>1000.0</v>
+      </c>
+      <c r="F5" s="9">
         <v>18000.0</v>
       </c>
+      <c r="N5" s="7"/>
     </row>
     <row r="6">
-      <c r="A6" s="6">
+      <c r="A6" s="2"/>
+      <c r="B6" s="8">
         <v>100000.0</v>
       </c>
-      <c r="B6" s="7">
+      <c r="C6" s="9">
         <v>10000.0</v>
       </c>
-      <c r="C6" s="7">
+      <c r="D6" s="9">
         <v>3.6481E7</v>
       </c>
-      <c r="D6" s="7">
+      <c r="E6" s="9">
+        <v>6000.0</v>
+      </c>
+      <c r="F6" s="9">
         <v>40000.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6">
+      <c r="A7" s="2"/>
+      <c r="B7" s="8">
         <v>200000.0</v>
       </c>
-      <c r="B7" s="7">
+      <c r="C7" s="9">
         <v>21000.0</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="7">
+      <c r="D7" s="9"/>
+      <c r="E7" s="9">
+        <v>2000.0</v>
+      </c>
+      <c r="F7" s="9">
         <v>80000.0</v>
       </c>
+      <c r="N7" s="7"/>
     </row>
     <row r="8">
-      <c r="A8" s="6">
+      <c r="A8" s="2"/>
+      <c r="B8" s="8">
         <v>300000.0</v>
       </c>
-      <c r="B8" s="7">
+      <c r="C8" s="9">
         <v>44000.0</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="7">
+      <c r="D8" s="9"/>
+      <c r="E8" s="9">
+        <v>3000.0</v>
+      </c>
+      <c r="F8" s="9">
         <v>120000.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6">
+      <c r="A9" s="2"/>
+      <c r="B9" s="8">
         <v>400000.0</v>
       </c>
-      <c r="B9" s="7">
+      <c r="C9" s="9">
         <v>70000.0</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="7">
+      <c r="D9" s="9"/>
+      <c r="E9" s="9">
+        <v>6000.0</v>
+      </c>
+      <c r="F9" s="9">
         <v>166000.0</v>
       </c>
+      <c r="N9" s="7"/>
     </row>
     <row r="10">
-      <c r="A10" s="6">
+      <c r="A10" s="2"/>
+      <c r="B10" s="8">
         <v>500000.0</v>
       </c>
-      <c r="B10" s="7">
+      <c r="C10" s="9">
         <v>64000.0</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="7">
+      <c r="D10" s="9"/>
+      <c r="E10" s="9">
+        <v>7000.0</v>
+      </c>
+      <c r="F10" s="9">
         <v>227000.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6">
+      <c r="A11" s="2"/>
+      <c r="B11" s="8">
         <v>600000.0</v>
       </c>
-      <c r="B11" s="7">
+      <c r="C11" s="9">
         <v>82000.0</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="7">
+      <c r="D11" s="9"/>
+      <c r="E11" s="9">
+        <v>8000.0</v>
+      </c>
+      <c r="F11" s="9">
         <v>260000.0</v>
       </c>
+      <c r="N11" s="7"/>
     </row>
     <row r="12">
-      <c r="A12" s="6">
+      <c r="A12" s="2"/>
+      <c r="B12" s="8">
         <v>700000.0</v>
       </c>
-      <c r="B12" s="7">
+      <c r="C12" s="9">
         <v>79000.0</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="7">
+      <c r="D12" s="9"/>
+      <c r="E12" s="9">
+        <v>8000.0</v>
+      </c>
+      <c r="F12" s="9">
         <v>320000.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6">
+      <c r="A13" s="2"/>
+      <c r="B13" s="8">
         <v>800000.0</v>
       </c>
-      <c r="B13" s="7">
+      <c r="C13" s="9">
         <v>93000.0</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="7">
+      <c r="D13" s="9"/>
+      <c r="E13" s="9">
+        <v>9000.0</v>
+      </c>
+      <c r="F13" s="9">
         <v>365000.0</v>
       </c>
+      <c r="N13" s="7"/>
     </row>
     <row r="14">
-      <c r="A14" s="6">
+      <c r="A14" s="2"/>
+      <c r="B14" s="8">
         <v>900000.0</v>
       </c>
-      <c r="B14" s="7">
+      <c r="C14" s="9">
         <v>113000.0</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="7">
+      <c r="D14" s="9"/>
+      <c r="E14" s="9">
+        <v>11000.0</v>
+      </c>
+      <c r="F14" s="9">
         <v>415000.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6">
+      <c r="A15" s="2"/>
+      <c r="B15" s="8">
         <v>1000000.0</v>
       </c>
-      <c r="B15" s="7">
+      <c r="C15" s="9">
         <v>169000.0</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="7">
+      <c r="D15" s="9"/>
+      <c r="E15" s="9">
+        <v>12000.0</v>
+      </c>
+      <c r="F15" s="9">
         <v>473000.0</v>
       </c>
+      <c r="N15" s="7"/>
     </row>
     <row r="16">
-      <c r="A16" s="6">
+      <c r="A16" s="2"/>
+      <c r="B16" s="8">
         <v>2000000.0</v>
       </c>
-      <c r="B16" s="7">
+      <c r="C16" s="9">
         <v>275000.0</v>
       </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="7">
+      <c r="D16" s="9"/>
+      <c r="E16" s="9">
+        <v>23000.0</v>
+      </c>
+      <c r="F16" s="9">
         <v>972000.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6">
+      <c r="A17" s="2"/>
+      <c r="B17" s="8">
         <v>3000000.0</v>
       </c>
-      <c r="B17" s="7">
+      <c r="C17" s="9">
         <v>435000.0</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="7">
+      <c r="D17" s="9"/>
+      <c r="E17" s="9">
+        <v>34000.0</v>
+      </c>
+      <c r="F17" s="9">
         <v>1501000.0</v>
       </c>
+      <c r="N17" s="7"/>
     </row>
     <row r="18">
-      <c r="A18" s="6">
+      <c r="A18" s="2"/>
+      <c r="B18" s="8">
         <v>4000000.0</v>
       </c>
-      <c r="B18" s="7">
+      <c r="C18" s="9">
         <v>580000.0</v>
       </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="7">
+      <c r="D18" s="9"/>
+      <c r="E18" s="9">
+        <v>49000.0</v>
+      </c>
+      <c r="F18" s="9">
         <v>2043000.0</v>
       </c>
     </row>
@@ -1518,212 +1712,271 @@
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="N19" s="7"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="3"/>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="2"/>
+      <c r="B21" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="C21" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="D21" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="E21" s="6" t="s">
         <v>4</v>
       </c>
+      <c r="F21" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" s="7"/>
     </row>
     <row r="22">
-      <c r="A22" s="6">
+      <c r="A22" s="2"/>
+      <c r="B22" s="8">
         <v>10000.0</v>
       </c>
-      <c r="B22" s="7">
+      <c r="C22" s="9">
         <v>1000.0</v>
       </c>
-      <c r="C22" s="7">
+      <c r="D22" s="9">
         <v>428000.0</v>
       </c>
-      <c r="D22" s="7">
+      <c r="E22" s="9">
+        <v>239000.0</v>
+      </c>
+      <c r="F22" s="9">
         <v>3000.0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6">
+      <c r="A23" s="2"/>
+      <c r="B23" s="8">
         <v>50000.0</v>
       </c>
-      <c r="B23" s="7">
+      <c r="C23" s="9">
         <v>5000.0</v>
       </c>
-      <c r="C23" s="7">
+      <c r="D23" s="9">
         <v>9507000.0</v>
       </c>
-      <c r="D23" s="7">
+      <c r="E23" s="9">
+        <v>6030000.0</v>
+      </c>
+      <c r="F23" s="9">
         <v>18000.0</v>
       </c>
+      <c r="N23" s="7"/>
     </row>
     <row r="24">
-      <c r="A24" s="6">
+      <c r="A24" s="2"/>
+      <c r="B24" s="8">
         <v>100000.0</v>
       </c>
-      <c r="B24" s="7">
+      <c r="C24" s="9">
         <v>10000.0</v>
       </c>
-      <c r="C24" s="7">
+      <c r="D24" s="9">
         <v>3.9435E7</v>
       </c>
-      <c r="D24" s="7">
+      <c r="E24" s="9">
+        <v>3.0759E7</v>
+      </c>
+      <c r="F24" s="9">
         <v>35000.0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6">
+      <c r="A25" s="2"/>
+      <c r="B25" s="8">
         <v>200000.0</v>
       </c>
-      <c r="B25" s="7">
+      <c r="C25" s="9">
         <v>22000.0</v>
       </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="7">
+      <c r="D25" s="10"/>
+      <c r="E25" s="9">
+        <v>1.23918E8</v>
+      </c>
+      <c r="F25" s="9">
         <v>76000.0</v>
       </c>
+      <c r="N25" s="7"/>
     </row>
     <row r="26">
-      <c r="A26" s="6">
+      <c r="A26" s="2"/>
+      <c r="B26" s="8">
         <v>300000.0</v>
       </c>
-      <c r="B26" s="7">
+      <c r="C26" s="9">
         <v>33000.0</v>
       </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="7">
+      <c r="D26" s="10"/>
+      <c r="E26" s="9">
+        <v>2.6058E8</v>
+      </c>
+      <c r="F26" s="9">
         <v>117000.0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6">
+      <c r="A27" s="2"/>
+      <c r="B27" s="8">
         <v>400000.0</v>
       </c>
-      <c r="B27" s="7">
+      <c r="C27" s="9">
         <v>60000.0</v>
       </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="7">
+      <c r="D27" s="10"/>
+      <c r="E27" s="9">
+        <v>4.49211E8</v>
+      </c>
+      <c r="F27" s="9">
         <v>164000.0</v>
       </c>
+      <c r="N27" s="7"/>
     </row>
     <row r="28">
-      <c r="A28" s="6">
+      <c r="A28" s="2"/>
+      <c r="B28" s="8">
         <v>500000.0</v>
       </c>
-      <c r="B28" s="7">
+      <c r="C28" s="9">
         <v>66000.0</v>
       </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="7">
+      <c r="D28" s="10"/>
+      <c r="E28" s="9">
+        <v>6.08331E8</v>
+      </c>
+      <c r="F28" s="9">
         <v>203000.0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6">
+      <c r="A29" s="2"/>
+      <c r="B29" s="8">
         <v>600000.0</v>
       </c>
-      <c r="B29" s="7">
+      <c r="C29" s="9">
         <v>71000.0</v>
       </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="7">
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="9">
         <v>246000.0</v>
       </c>
+      <c r="N29" s="7"/>
     </row>
     <row r="30">
-      <c r="A30" s="6">
+      <c r="A30" s="2"/>
+      <c r="B30" s="8">
         <v>700000.0</v>
       </c>
-      <c r="B30" s="7">
+      <c r="C30" s="9">
         <v>82000.0</v>
       </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="7">
+      <c r="D30" s="10"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9">
         <v>294000.0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6">
+      <c r="A31" s="2"/>
+      <c r="B31" s="8">
         <v>800000.0</v>
       </c>
-      <c r="B31" s="7">
+      <c r="C31" s="9">
         <v>105000.0</v>
       </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="7">
+      <c r="D31" s="10"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9">
         <v>348000.0</v>
       </c>
+      <c r="N31" s="7"/>
     </row>
     <row r="32">
-      <c r="A32" s="6">
+      <c r="A32" s="2"/>
+      <c r="B32" s="8">
         <v>900000.0</v>
       </c>
-      <c r="B32" s="7">
+      <c r="C32" s="9">
         <v>117000.0</v>
       </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="7">
+      <c r="D32" s="10"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9">
         <v>399000.0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6">
+      <c r="A33" s="2"/>
+      <c r="B33" s="8">
         <v>1000000.0</v>
       </c>
-      <c r="B33" s="7">
+      <c r="C33" s="9">
         <v>163000.0</v>
       </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="7">
+      <c r="D33" s="10"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9">
         <v>444000.0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6">
+      <c r="A34" s="2"/>
+      <c r="B34" s="8">
         <v>2000000.0</v>
       </c>
-      <c r="B34" s="7">
+      <c r="C34" s="9">
         <v>308000.0</v>
       </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="7">
+      <c r="D34" s="10"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9">
         <v>949000.0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6">
+      <c r="A35" s="2"/>
+      <c r="B35" s="8">
         <v>3000000.0</v>
       </c>
-      <c r="B35" s="7">
+      <c r="C35" s="9">
         <v>457000.0</v>
       </c>
-      <c r="C35" s="8"/>
-      <c r="D35" s="7">
+      <c r="D35" s="10"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9">
         <v>1432000.0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6">
+      <c r="A36" s="2"/>
+      <c r="B36" s="8">
         <v>4000000.0</v>
       </c>
-      <c r="B36" s="7">
+      <c r="C36" s="9">
         <v>589000.0</v>
       </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="7">
+      <c r="D36" s="10"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9">
         <v>1932000.0</v>
       </c>
     </row>
@@ -1732,210 +1985,269 @@
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" s="3"/>
+      <c r="A38" s="2"/>
+      <c r="B38" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="2"/>
+      <c r="B39" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="C39" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="D39" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="E39" s="6" t="s">
         <v>4</v>
       </c>
+      <c r="F39" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="N39" s="11"/>
+      <c r="O39" s="11"/>
     </row>
     <row r="40">
-      <c r="A40" s="6">
+      <c r="A40" s="2"/>
+      <c r="B40" s="8">
         <v>10000.0</v>
       </c>
-      <c r="B40" s="7">
+      <c r="C40" s="9">
         <v>3000.0</v>
       </c>
-      <c r="C40" s="7">
-        <v>562333.0</v>
-      </c>
-      <c r="D40" s="7">
+      <c r="D40" s="9">
+        <v>614.0</v>
+      </c>
+      <c r="E40" s="9">
+        <v>156667.0</v>
+      </c>
+      <c r="F40" s="9">
         <v>4333.0</v>
       </c>
+      <c r="N40" s="7"/>
     </row>
     <row r="41">
-      <c r="A41" s="6">
+      <c r="A41" s="2"/>
+      <c r="B41" s="8">
         <v>50000.0</v>
       </c>
-      <c r="B41" s="7">
+      <c r="C41" s="9">
         <v>16333.0</v>
       </c>
-      <c r="C41" s="7">
-        <v>1.6160667E7</v>
-      </c>
-      <c r="D41" s="7">
+      <c r="D41" s="9">
+        <v>15277.667</v>
+      </c>
+      <c r="E41" s="9">
+        <v>5123333.0</v>
+      </c>
+      <c r="F41" s="9">
         <v>22333.0</v>
       </c>
+      <c r="N41" s="7"/>
+      <c r="O41" s="12"/>
     </row>
     <row r="42">
-      <c r="A42" s="6">
+      <c r="A42" s="2"/>
+      <c r="B42" s="8">
         <v>100000.0</v>
       </c>
-      <c r="B42" s="7">
+      <c r="C42" s="9">
         <v>38667.0</v>
       </c>
-      <c r="C42" s="8"/>
-      <c r="D42" s="7">
+      <c r="D42" s="9">
+        <v>75358.333</v>
+      </c>
+      <c r="E42" s="9">
+        <v>2.2318E7</v>
+      </c>
+      <c r="F42" s="9">
         <v>49333.0</v>
       </c>
+      <c r="N42" s="7"/>
+      <c r="O42" s="12"/>
     </row>
     <row r="43">
-      <c r="A43" s="6">
+      <c r="A43" s="2"/>
+      <c r="B43" s="8">
         <v>200000.0</v>
       </c>
-      <c r="B43" s="7">
+      <c r="C43" s="9">
         <v>81333.0</v>
       </c>
-      <c r="C43" s="8"/>
-      <c r="D43" s="7">
+      <c r="D43" s="9">
+        <v>316459.0</v>
+      </c>
+      <c r="E43" s="9">
+        <v>7.8438667E7</v>
+      </c>
+      <c r="F43" s="9">
         <v>107000.0</v>
       </c>
+      <c r="N43" s="7"/>
+      <c r="O43" s="12"/>
     </row>
     <row r="44">
-      <c r="A44" s="6">
+      <c r="A44" s="2"/>
+      <c r="B44" s="8">
         <v>300000.0</v>
       </c>
-      <c r="B44" s="7">
+      <c r="C44" s="9">
         <v>124333.0</v>
       </c>
-      <c r="C44" s="8"/>
-      <c r="D44" s="7">
+      <c r="D44" s="13"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9">
         <v>176000.0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6">
+      <c r="A45" s="2"/>
+      <c r="B45" s="8">
         <v>400000.0</v>
       </c>
-      <c r="B45" s="7">
+      <c r="C45" s="9">
         <v>159333.0</v>
       </c>
-      <c r="C45" s="8"/>
-      <c r="D45" s="7">
+      <c r="D45" s="13"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9">
         <v>243000.0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6">
+      <c r="A46" s="2"/>
+      <c r="B46" s="8">
         <v>500000.0</v>
       </c>
-      <c r="B46" s="7">
+      <c r="C46" s="9">
         <v>218333.0</v>
       </c>
-      <c r="C46" s="8"/>
-      <c r="D46" s="7">
+      <c r="D46" s="13"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9">
         <v>316667.0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6">
+      <c r="A47" s="2"/>
+      <c r="B47" s="8">
         <v>600000.0</v>
       </c>
-      <c r="B47" s="7">
+      <c r="C47" s="9">
         <v>245333.0</v>
       </c>
-      <c r="C47" s="8"/>
-      <c r="D47" s="7">
+      <c r="D47" s="13"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9">
         <v>379000.0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="6">
+      <c r="A48" s="2"/>
+      <c r="B48" s="8">
         <v>700000.0</v>
       </c>
-      <c r="B48" s="7">
+      <c r="C48" s="9">
         <v>298667.0</v>
       </c>
-      <c r="C48" s="8"/>
-      <c r="D48" s="7">
+      <c r="D48" s="13"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9">
         <v>463667.0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6">
+      <c r="A49" s="2"/>
+      <c r="B49" s="8">
         <v>800000.0</v>
       </c>
-      <c r="B49" s="7">
+      <c r="C49" s="9">
         <v>353000.0</v>
       </c>
-      <c r="C49" s="8"/>
-      <c r="D49" s="7">
+      <c r="D49" s="13"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9">
         <v>540333.0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6">
+      <c r="A50" s="2"/>
+      <c r="B50" s="8">
         <v>900000.0</v>
       </c>
-      <c r="B50" s="7">
+      <c r="C50" s="9">
         <v>396333.0</v>
       </c>
-      <c r="C50" s="8"/>
-      <c r="D50" s="7">
+      <c r="D50" s="13"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9">
         <v>619667.0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6">
+      <c r="A51" s="2"/>
+      <c r="B51" s="8">
         <v>1000000.0</v>
       </c>
-      <c r="B51" s="7">
+      <c r="C51" s="9">
         <v>431333.0</v>
       </c>
-      <c r="C51" s="8"/>
-      <c r="D51" s="7">
+      <c r="D51" s="13"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9">
         <v>705333.0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6">
+      <c r="A52" s="2"/>
+      <c r="B52" s="8">
         <v>2000000.0</v>
       </c>
-      <c r="B52" s="7">
+      <c r="C52" s="9">
         <v>916000.0</v>
       </c>
-      <c r="C52" s="8"/>
-      <c r="D52" s="7">
+      <c r="D52" s="13"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9">
         <v>1593000.0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6">
+      <c r="A53" s="2"/>
+      <c r="B53" s="8">
         <v>3000000.0</v>
       </c>
-      <c r="B53" s="7">
+      <c r="C53" s="9">
         <v>1422333.0</v>
       </c>
-      <c r="C53" s="8"/>
-      <c r="D53" s="7">
+      <c r="D53" s="13"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9">
         <v>2616000.0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6">
+      <c r="A54" s="2"/>
+      <c r="B54" s="8">
         <v>4000000.0</v>
       </c>
-      <c r="B54" s="7">
+      <c r="C54" s="9">
         <v>1921333.0</v>
       </c>
-      <c r="C54" s="8"/>
-      <c r="D54" s="7">
+      <c r="D54" s="13"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9">
         <v>3631000.0</v>
       </c>
     </row>
